--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>93418</v>
+        <v>93421</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
